--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Prompt Engineering, S3, Glue, Redshift, Apache Airflow, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, LLaMA, Gemini, TensorFlow, PyTorch, AWS SageMaker, Azure ML, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc923db635e0445</t>
+          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Developer | Wilmington/New York, US</t>
+          <t>Campus - Technology Program Intern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Prompt Engineering, Redshift, Kinesis, CI/CD, Terraform, Git, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3055aff36999475</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer | New York, US</t>
+          <t>Infrastructure and Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0c058e2336a74</t>
+          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>PhD Intern, AI/ML/NLP Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, NLP Engineer, Generative AI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a2a9be0716c272</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd81985cd24d1b8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake, Redshift</t>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a21382364703b4</t>
+          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, EC2, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5f76bfb12df950</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Glue, Redshift, Jenkins, Git, Redshift, PySpark</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850a20cd8ff834db</t>
+          <t>https://www.indeed.com/viewjob?jk=04cca04733a65203</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Full Stack Innovations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Glue, Redshift, Jenkins, Git, Redshift, PySpark</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b6e83cac419bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
         </is>
       </c>
     </row>
@@ -753,55 +753,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>RAG, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c62de20f503598</t>
+          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Science (Master’s degree) (2027 Grads)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, Keras, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e630b930a457c580</t>
+          <t>https://www.indeed.com/viewjob?jk=60ae0a2d52563853</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Scientist (Master's Degree) Internship</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, Keras, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c632411cd4b849</t>
+          <t>https://www.indeed.com/viewjob?jk=4a33618698609ad2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Data Lake, Git, NoSQL, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Databricks, Power BI, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a6c6ab5ea1b17</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2a750862b7a12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Python Intern - Summer 2027</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Copilot, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1a7457eaca44f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3bd230fd306798c9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Senior Software Engineer, Fleet Intelligence Backend</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ec949e0bf8d6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e89160fd118877b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Data Lake &amp; Data Warehouse Solutions)</t>
+          <t>Software Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7ddb65eff0fc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=279de2cac41220bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Designer, Automation</t>
+          <t>Senior Software Engineer, Hybrid, Milpitas, CA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab48f6a21f827e3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd8609fbf73d8d98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,637 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19840c695617287</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Data Lake, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b87595056b9c77d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Marmon Foodservice Technologies</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Carol Stream, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Data Lake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4976e7c60f29ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>imgIX</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, FastAPI, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e514d5b5dceb6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Legal Tech &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>The Lemon Pros, LLP</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Beverly Hills, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9121da6207426f72</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Marlborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=743403320782202e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Marlborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c67d3baa353c6cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Enterprise AI Enablement Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Moderna</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Athena, Redshift, CI/CD, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd857ebbecc62a2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf41084edbe6859</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Automation Tester</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53d3819259eb1efe</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MS Fabric Solution Architect</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Data Lake, Git, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c253678ec07341</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>OCLC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Dublin, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b28ee7222032d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MS Fabric Solution Architect</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Data Lake, Git, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c5705c294cdab3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Vforce Infotech</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d7931bd8fcf2b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Engineer II - MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e11a66c74b77cc63</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Databricks, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23a6d160d199bf90</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Junior Data Migration Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d04fa659565fd9fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr Architect-Professional Services ( USA Remote)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Alteryx</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6c543d3897fae</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2027 DevOps Summer Internship</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Advanced Space</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c08c3d954259f57</t>
+          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Ziply Fiber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>35.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, LLaMA, Gemini, TensorFlow, PyTorch, AWS SageMaker, Azure ML, BigQuery</t>
+          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f24e0707a64972</t>
+          <t>https://www.indeed.com/viewjob?jk=a6405304b5156b40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Campus - Technology Program Intern</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, Kinesis, CI/CD, Terraform, Git, Redshift, Tableau, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, S3, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6387e06d593380</t>
+          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Infrastructure and Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, S3, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97cc90da58e4bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PhD Intern, AI/ML/NLP Engineer</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, NLP Engineer, Generative AI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd81985cd24d1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b55a7fd76f93036a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, AWS SageMaker, Azure ML, S3, MLflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31817120a8680684</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Databricks, Kafka, Hadoop, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcc3b59ee444760</t>
+          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr DevOps Engineer-Remote-(If in MN then Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04cca04733a65203</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8ba85f428d858</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack Innovations</t>
+          <t>Senior AI Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2c2e254df88efd</t>
+          <t>https://www.indeed.com/viewjob?jk=22a277abeacdd536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433e986b684f5853</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae0c5b694b79cf5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Science (Master’s degree) (2027 Grads)</t>
+          <t>Senior AI Platform Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Keras, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ae0a2d52563853</t>
+          <t>https://www.indeed.com/viewjob?jk=81be29d177e4b151</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist (Master's Degree) Internship</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Computer Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Keras, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, XGBoost, LightGBM, Git, Snowflake, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a33618698609ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=f95df4d8aa79c968</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>The Port Authority of New York and New Jersey</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Databricks, Power BI, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Synapse, Databricks, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2a750862b7a12</t>
+          <t>https://www.indeed.com/viewjob?jk=863ea52e07e6d1ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Intern - Summer 2027</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medpace</t>
+          <t>Computer Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Git, Snowflake, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bd230fd306798c9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2244a864659f73</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Fleet Intelligence Backend</t>
+          <t>Senior Associate - Salesforce Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89160fd118877b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b2973623fff7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - AI/ML</t>
+          <t>Senior Associate - Salesforce Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279de2cac41220bd</t>
+          <t>https://www.indeed.com/viewjob?jk=65e39ada6a4d71ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Hybrid, Milpitas, CA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Cartersville, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8609fbf73d8d98</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5bc3f59004bbf5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Git, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579c0bfa3c66935</t>
+          <t>https://www.indeed.com/viewjob?jk=52ccbb210aa13cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f900a55078eba8df</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Manufacturing Software Research Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ziply Fiber</t>
+          <t>CCAM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Disputanta, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.6</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, AKS</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Git, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6405304b5156b40</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2afda1221363c9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Data Scientist III, Behavioral Marketing Analytics &amp; Customer Insights</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, S3, Docker</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d23aa8bd88eaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6207e32221b5cea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Data Scientist III, Behavioral Marketing Analytics &amp; Customer Insights</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, S3, Docker</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40dcc3ad9f96288f</t>
+          <t>https://www.indeed.com/viewjob?jk=5721564890e574f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55a7fd76f93036a</t>
+          <t>https://www.indeed.com/viewjob?jk=afc962a0a78e4dda</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Developer I - BI &amp; Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Azure ML, S3, MLflow, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, TensorFlow, Tableau, Power BI, MicroStrategy, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7a33b4467a0975</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8ee8bd1bee6ae7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Test Automation Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Databricks, Kafka, Hadoop, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f880518e0811cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5602304c243436</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer-Remote-(If in MN then Hybrid)</t>
+          <t>Senior Model Developer 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>INISGHT2PROFIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8ba85f428d858</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6d8d96af8f598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer (DevOps)</t>
+          <t>Senior Data Analyst – Certification 3.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,357 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a277abeacdd536</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb486ba5641120d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer (DevOps)</t>
+          <t>Blockchain Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Itransition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Docker, CI/CD, Kafka, PostgreSQL, MongoDB, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae0c5b694b79cf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer (DevOps)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81be29d177e4b151</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Computer Services</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, LightGBM, Git, Snowflake, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f95df4d8aa79c968</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The Port Authority of New York and New Jersey</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Synapse, Databricks, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=863ea52e07e6d1ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Computer Services</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Snowflake, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2244a864659f73</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Associate - Salesforce Developer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b2973623fff7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Associate - Salesforce Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65e39ada6a4d71ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Qcells</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Cartersville, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5bc3f59004bbf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52ccbb210aa13cd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f900a55078eba8df</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fe443ce4861ed7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Manufacturing Software Research Engineer</t>
+          <t>SR Data Scientist, Rental</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CCAM</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Disputanta, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Git, Matplotlib, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Git, Snowflake, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,287 +496,147 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2afda1221363c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist III, Behavioral Marketing Analytics &amp; Customer Insights</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Finastra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6207e32221b5cea</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5bd7c38914ff28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist III, Behavioral Marketing Analytics &amp; Customer Insights</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Curant Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5721564890e574f7</t>
+          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Children's National Hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc962a0a78e4dda</t>
+          <t>https://www.indeed.com/viewjob?jk=02fcd21c754ac053</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Developer I - BI &amp; Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Xactus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Tableau, Power BI, MicroStrategy, Python, SQL, R, Java, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8ee8bd1bee6ae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602304c243436</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Model Developer 1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>INISGHT2PROFIT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6d8d96af8f598</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst – Certification 3.0</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>The Joint Commission</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb486ba5641120d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Blockchain Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Itransition</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Docker, CI/CD, Kafka, PostgreSQL, MongoDB, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fe443ce4861ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=7608d134da177f1f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SR Data Scientist, Rental</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Git, Snowflake, BigQuery, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d923de67e31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer II - ML and Observability</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finastra</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5bd7c38914ff28</t>
+          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Curant Health</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, CI/CD, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396bc3d72f57166d</t>
+          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Children's National Hospital</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Databricks, Redshift, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fcd21c754ac053</t>
+          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xactus</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, S3, Glue, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,252 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7608d134da177f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Application Developer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>endava</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Document Intelligence</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b01d21c216bd79e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SRE Software Systems Engineer IV</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sabre</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Kubernetes, Apache Airflow, Terraform, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc85ada3c8da5b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Workwhile</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Git, BigQuery, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1ccdebd9dd28a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e583ebc0a2b90e17</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Hugging Face, BigQuery, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052b239d50574588</t>
+          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - ML and Observability</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Git</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655a9a6d34f5dbef</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b483b64afeb3e0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=838a3a0e43fd5f9f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Databricks, Redshift, Power BI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f5be0e78b3ab5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f113fef6ee611e08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177171af39893b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Snowflake and Lakehouse</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, Hugging Face, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189c2d0348ec6158</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e4f57f20c8e6aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4e67065f473c15</t>
+          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Document Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>TheGuarantors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d21c216bd79e6</t>
+          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRE Software Systems Engineer IV</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sabre</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Kubernetes, Apache Airflow, Terraform, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, S3, Redshift, CI/CD, Jenkins, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc85ada3c8da5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTM Engineer</t>
+          <t>Software Engineer (Client Solutions)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Workwhile</t>
+          <t>AZX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Git, BigQuery, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1ccdebd9dd28a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0126a4664af507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Hartford)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,322 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754a44c7dfc4ab06</t>
+          <t>https://www.indeed.com/viewjob?jk=f10567678dabed8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Senior</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, LLaMA, Mistral, BigQuery, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=221948c3bac510c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Owens &amp; Minor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Glen Allen, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, BigQuery, PySpark, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=162db89ebe483530</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>innoVet Health, LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>11.1</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e583ebc0a2b90e17</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a53ba237c911865</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Python Full Stack Security Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d598ebafd3b8283</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Matrix International Financial Services</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Dataflow, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Front End Developer - JavaScript</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2305e15e333aba60</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior eCommerce Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Airgas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Radnor, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d0a08593d97174</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Neara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24adabe75eea8b28</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Hugging Face, BigQuery, FastAPI, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c27f1fa1de3f62</t>
+          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>28.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1ea51976266b71</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838a3a0e43fd5f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113fef6ee611e08</t>
+          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>28.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe39bc39c0dfdae9</t>
+          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>28.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, Hugging Face, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e4f57f20c8e6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java Backend &amp; AI Engineer – Wealth Management</t>
+          <t>Agentic AI Architect-Anthropic-US East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>28.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a59b3cdfe58cc35</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TheGuarantors</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>28.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497fe5a6dfd14dec</t>
+          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Agentic AI Architect-Anthropic-US West</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Redshift, CI/CD, Jenkins, Git, Redshift, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18f276c9b0d4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (Client Solutions)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AZX</t>
+          <t>OneDome</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, BigQuery, Synapse, Kinesis, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0126a4664af507</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, BigQuery, Docker, Kubernetes, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f10567678dabed8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, LLaMA, Mistral, BigQuery, BigQuery, Python, R</t>
+          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221948c3bac510c2</t>
+          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Owens &amp; Minor</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, BigQuery, PySpark, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162db89ebe483530</t>
+          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a53ba237c911865</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Full Stack Security Engineer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d598ebafd3b8283</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d94581ef25281ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Front End Developer - JavaScript</t>
+          <t>Forward Deployed Engineer (FDE) - Data 360</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2305e15e333aba60</t>
+          <t>https://www.indeed.com/viewjob?jk=f25565664c7eee01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior eCommerce Operations Analyst</t>
+          <t>Solution Engineer - Federal Civilian</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Airgas</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, S3, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d0a08593d97174</t>
+          <t>https://www.indeed.com/viewjob?jk=1a523e2f6ac1f3c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d2a1a315111b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Neara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,21 +1147,931 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peoples Gas System</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, AKS, Snowflake, Databricks, Redshift, Kafka, Hadoop, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Application Developer/Reverse Engineer III</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c18fe9c94d508c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5128db39c6adbd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Observability Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NCR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb41d26fb40ba90</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vulnerability security tester - 12+ years Local</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ParsoftLLC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=146a22bfe37cb2e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BlueCross BlueShield of Tennessee</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e2c5523f16646c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bitsight</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1817944323f9aff</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c09b33e4e9a3e25a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Charging &amp; Energy Services</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d61a3f7a3b8118</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. GEN AI Python Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hanover, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, FastAPI, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5c88669679143e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>INFINITY HOME SERVICES</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Docker, AKS, CI/CD, Terraform, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INflow Federal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Springfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329a300f3ddcecf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Perception Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c964d6344aac12b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DATA SCIENTIST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SANTEE COOPER</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Moncks Corner, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=507f7adb3840f6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Product Owner - Geoscience &amp; Reservoir</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DIAMONDBACK ENERGY</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Midland, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24adabe75eea8b28</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41643d5099da1cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd2e31872ef1cdeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c0b3e756bb06361</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33deb6dadc9194b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aec1b509fa563112</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6120a8e6cf4afab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a90827c0e5167c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af0b58b4383492a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bf328f6261b6dc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad62fdc00aab36b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer – AI Platforms</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3a7996947859cbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Big Data Engineer - Python/Scala, Spark, Hadoop</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30c6ea34313bc9f5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-25.xlsx
+++ b/daily_matches/job_matches_2026-08-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>AAA Auto Club Enterprises</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Data Scientist, RAG, Cortex, TensorFlow, PyTorch, S3, EC2, Redshift, BigQuery, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451eef560601ded5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e80b460b21ce73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3ee7b1db2cccd5</t>
+          <t>https://www.indeed.com/viewjob?jk=181a31f219accf44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d1d5763df13b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e60dd927ca9f910c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.9</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03deb24662c2d57b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3a61d4ef5518a8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Senior Developer- Snowflake Cortex AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.9</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Prompt Engineering, Cortex, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f191710314c15359</t>
+          <t>https://www.indeed.com/viewjob?jk=fdcaa5bb36a01e40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Data Scientist / AI Specialist (Junior to Mid-Level)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Refocus Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.9</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d939da0bcff1af</t>
+          <t>https://www.indeed.com/viewjob?jk=924529933cf335d0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US East</t>
+          <t>Machine Learning Engineer GCP Vertex AI Apache Iceberg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.9</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Machine Learning Engineer, RAG, GCP Vertex AI, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e2c8f86b9525b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4819706c3ee3c8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Sr Talend Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.9</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Snowflake, Redshift, Hadoop, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082b971e34568c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=743665ae918f4a0c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Anthropic-US West</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.9</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, S3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d52f1deebd9cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2579aa4dcb8527e9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>JobID_Data Scientist826</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OneDome</t>
+          <t>Involgix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, BigQuery, Synapse, Kinesis, Terraform</t>
+          <t>Data Scientist, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7886502273f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3278684e3aeb2fc5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) — Agentforce Orchestration</t>
+          <t>Applied AI Engineer/Full stack App Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Farmers Insurance Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, BigQuery, Docker, Kubernetes, Terraform, Git, Snowflake</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, AKS, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f504c00cfca80e26</t>
+          <t>https://www.indeed.com/viewjob?jk=8111adc122d33c26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Software Engineer (Backend-Focused)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>AZX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591d7ae91cb2eb99</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8fa738da4c8f7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Software Engineer Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503f43f12c92318e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6bc6108de9de34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8df85ea0e8639</t>
+          <t>https://www.indeed.com/viewjob?jk=abe6d49f2090e301</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Health Plan Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, LangChain, RAG, MLflow, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb744e0bd727a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dac33958a2fe20a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Applied AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, Azure ML Studio, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>Generative AI, LangChain, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Kafka, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe7d5bfc808f782</t>
+          <t>https://www.indeed.com/viewjob?jk=119fa3aa40cc75f8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) - Data 360</t>
+          <t>DevOps &amp; Platform Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25565664c7eee01</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0a699f65bddf68</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solution Engineer - Federal Civilian</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a523e2f6ac1f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=242eab96e596ec8c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist, Charging &amp; Energy Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a9353ab1875600</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbc2bb3bdaa37ed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Junior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271bbcd0786a6bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c4cad7e65f0f71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Peoples Gas System</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Redshift, AKS, Snowflake, Databricks, Redshift, Kafka, Hadoop, NoSQL, Python</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32754dc82fcb92a</t>
+          <t>https://www.indeed.com/viewjob?jk=37423782719e04ee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Application Developer/Reverse Engineer III</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c18fe9c94d508c</t>
+          <t>https://www.indeed.com/viewjob?jk=5575d311b6553ff3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Remote</t>
+          <t>Senior Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128db39c6adbd2</t>
+          <t>https://www.indeed.com/viewjob?jk=25a38e1e8e492fa4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Observability Engineer</t>
+          <t>Senior Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NCR</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R</t>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb41d26fb40ba90</t>
+          <t>https://www.indeed.com/viewjob?jk=1cde486178e3b477</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vulnerability security tester - 12+ years Local</t>
+          <t>Senior Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ParsoftLLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146a22bfe37cb2e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1315c64b69550240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Systems Operations Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Python, R</t>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2c5523f16646c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea40ff5d26fc815e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Wrench.ai Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1817944323f9aff</t>
+          <t>https://www.indeed.com/viewjob?jk=83be4ed684048bae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09b33e4e9a3e25a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec4caa05b6a05ee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist, Charging &amp; Energy Services</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, S3, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d61a3f7a3b8118</t>
+          <t>https://www.indeed.com/viewjob?jk=784101a0b788d5b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. GEN AI Python Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, FastAPI, CI/CD, Git, Python, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c88669679143e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce79ef9cdbb6e910</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Innovation Delivery Platform Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INFINITY HOME SERVICES</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, AKS, CI/CD, Terraform, PostgreSQL, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834def53d716402e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb11c4f7226c9f94</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Columbus)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INflow Federal</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329a300f3ddcecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdad2f2d7148761c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Perception Engineer</t>
+          <t>Senior Software Engineer, Datacenter Operations Platform Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CRUSOE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c964d6344aac12b9</t>
+          <t>https://www.indeed.com/viewjob?jk=228e8eed3c3dc007</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SANTEE COOPER</t>
+          <t>Vendelux</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Moncks Corner, SC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507f7adb3840f6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7fff232d7439055c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Product Owner - Geoscience &amp; Reservoir</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Vendelux</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Midland, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41643d5099da1cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bfcc1e13f1f432e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vendelux</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2e31872ef1cdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=b99aada7d83d0ab4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vendelux</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0b3e756bb06361</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd6ad08eb70fe67</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Associate - NASA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33deb6dadc9194b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c77d0865eb1cf492</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,252 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec1b509fa563112</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6120a8e6cf4afab4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08a90827c0e5167c</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b58b4383492a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf328f6261b6dc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad62fdc00aab36b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer – AI Platforms</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a7996947859cbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Big Data Engineer - Python/Scala, Spark, Hadoop</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30c6ea34313bc9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbdd0bae017d3e</t>
         </is>
       </c>
     </row>
